--- a/normalizador_posiciones.xlsx
+++ b/normalizador_posiciones.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KIK_3\OneDrive\Documentos\QUALITY RADIADORES\compatibilidades\PROYECTO_MASTER_COMPATIBILIDADES\Compa\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/30f5266fa37582a4/Documentos/QUALITY RADIADORES/compatibilidades/PROYECTO_MASTER_COMPATIBILIDADES/Compa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49325908-C8C4-4969-BE8C-14A1797C1779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{49325908-C8C4-4969-BE8C-14A1797C1779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BFB20A5-F6D7-4693-A972-08DDA43A5705}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9D7395E0-0D39-4E61-82A8-1741618EDED8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="83">
   <si>
     <t>Entrada</t>
   </si>
@@ -282,6 +282,12 @@
   </si>
   <si>
     <t>Inferior, Superior</t>
+  </si>
+  <si>
+    <t>INTERNA</t>
+  </si>
+  <si>
+    <t>EXTERNA</t>
   </si>
 </sst>
 </file>
@@ -337,7 +343,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -345,7 +351,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -361,6 +366,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -680,7 +689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CEBACD8-C7D2-4B49-9323-6430B57ACB9F}">
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:B66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
@@ -1163,7 +1172,7 @@
       <c r="A60" t="s">
         <v>73</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1197,6 +1206,22 @@
       </c>
       <c r="B64" t="s">
         <v>80</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>81</v>
+      </c>
+      <c r="B65" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>82</v>
+      </c>
+      <c r="B66" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
